--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,45 +787,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16888772</v>
+        <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6800 m OSO Storgranliden, Nb</t>
+          <t>Storgranliden, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759111</v>
+        <v>759160</v>
       </c>
       <c r="R3" t="n">
-        <v>7258191</v>
+        <v>7258177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskog naturvärdesinventering, inventerare: Gustaf Dal</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,18 +881,236 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136759961</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16888772</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6800 m OSO Storgranliden, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>759111</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7258191</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-10-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare: Gustaf Dal</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/16888772</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136759962</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80589</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storgranliden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>759196</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7258125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759962</t>
         </is>
       </c>
     </row>
@@ -896,6 +1118,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38461-2026 artfynd.xlsx
+++ b/artfynd/A 38461-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136759961</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136759962</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
